--- a/docs/03_詳細設計/03_テーブル設計/KF-DD-TBL-08_holidays_祝日_テーブル詳細設計書.xlsx
+++ b/docs/03_詳細設計/03_テーブル設計/KF-DD-TBL-08_holidays_祝日_テーブル詳細設計書.xlsx
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B3:C22"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -562,6 +562,8 @@
     <col width="60" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
+    <row r="1"/>
+    <row r="2"/>
     <row r="3">
       <c r="B3" s="1" t="inlineStr">
         <is>
@@ -576,6 +578,8 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
+    <row r="6"/>
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
@@ -644,7 +648,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.2</t>
         </is>
       </c>
     </row>
@@ -684,12 +688,14 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
+    <row r="17"/>
     <row r="18">
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>本書の位置づけ：KF-DD-003 は全 9 テーブルの総覧（ER 図・CRUD マトリクス・規約）。本書はそのうち holidays を、列・制約・索引・アクセスパターン・排他・運用まで実装/運用できる粒度で詳細化したもの。
-列・型・NULL・既定値・制約・索引・トリガは backend/schema.sql（KF-DD-003 v2.0 版。PostgreSQL 18）を解析して自動生成している（手書きで写していない）。アクセスパターンは ONL-001〜022 の規格（tables / mapping / sql）と BAT-001〜003 から自動抽出した。
-章番号は全テーブル共通。「4.状態遷移・コード値」は状態・コード値を持つ表（users / leave_types / requests / approval_steps / notifications）のみ作成している。</t>
+          <t>本書の位置づけ：KF-DD-003 は全 10 テーブルの総覧（ER 図・CRUD マトリクス・規約）。本書はそのうち holidays を、列・制約・索引・アクセスパターン・排他・運用まで実装/運用できる粒度で詳細化したもの。
+列・型・NULL・既定値・制約・索引・トリガは backend/src/main/resources/db/migration の V1__init_schema.sql・V4__attendance_breaks.sql・V5__break_correction_request.sql（Flyway。KF-DD-003 v2.3 版。PostgreSQL 18）を解析して自動生成している（手書きで写していない）。アクセスパターンは ONL-001〜023 の規格（tables / mapping / sql）に、2026/10/05 のコード（AttendanceService / RequestService / ApprovalService / DepartmentController）から起こした ONL-024〜026（休憩・離席の開始・終了、部署一覧。番号は仮）と既存処理の追加アクセスを重ね、BAT-001〜003 と合わせて抽出した。
+章番号は全テーブル共通。「4.状態遷移・コード値」は状態・コード値を持つ表（users / leave_types / requests / approval_steps / notifications / attendance_breaks）のみ作成している。</t>
         </is>
       </c>
     </row>
@@ -712,7 +718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F27"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -723,6 +729,7 @@
     <col width="10" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
@@ -767,15 +774,15 @@
       <c r="E4" s="9" t="n"/>
       <c r="F4" s="10" t="n"/>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="63" customHeight="1">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>年次メンテナンス</t>
+          <t>年次メンテナンス（毎年の追加）</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>毎年 2 月頃に翌年分（内閣府の祝日一覧）を ONL-016 で登録する運用を定義する。登録漏れは営業日数の過大計算につながる。</t>
+          <t>初期データ（V2・V3）は 2028-12-31 まで。毎年、翌年分（内閣府の祝日一覧、年末年始 12/29〜1/3 の会社休日）を ONL-016 で登録する（目安：2 月頃に翌年分）。2029 年 1 月の元日（1/1）と年始の会社休日（1/2・1/3）は 2028 年内に登録しておくこと（V3 には含まれない）。登録漏れは営業日数の過大計算につながる（10章の最終登録日と翌年分の確認 SQL で確認）。新規に構築する環境にも同じ祝日を入れたい場合は、同内容を V6 以降の新しいマイグレーション（例：V6__seed_holidays_2029.sql。INSERT … ON CONFLICT (holiday_date) DO NOTHING）にも追加する。V2・V3 自体は適用後に編集しない。ONL-016 で登録した分は DB にしか残らず、Flyway では再現されない。</t>
         </is>
       </c>
       <c r="C5" s="9" t="n"/>
@@ -783,15 +790,15 @@
       <c r="E5" s="9" t="n"/>
       <c r="F5" s="10" t="n"/>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="77.5" customHeight="1">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>初期データ</t>
+          <t>初期データ（V2・V3）</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>schema.sql に祝日データは無い（空）。</t>
+          <t>V2：2026-01-01〜2027-12-31 の 43 件（2026 年 21 件＝国民の祝日 18＋会社休日 3、2027 年 22 件＝国民の祝日 17＋会社休日 5）。V3：2028 年 21 件（国民の祝日 16＋会社休日 5。振替休日なし）。V3 の日付は規則に基づく推算値で、内閣府の公表値との照合は未実施（課題 H-4）。冪等性：どちらも ON CONFLICT (holiday_date) DO NOTHING のため、再実行しても件数は増えず、同じ日付が先にある行（ONL-016 で登録済み）は上書きされない。Flyway は各版を 1 回だけ実行するが、既存の開発 DB（baseline-on-migrate で V1 から取り込んだ DB）に祝日が登録済みでも失敗しない。DO NOTHING で飛ばした行も IDENTITY の採番値は進むため、id に欠番が出ることがある。祝日の変更（制度改正等）は ONL-016 の削除→再登録で行い、V2・V3 は編集しない。</t>
         </is>
       </c>
       <c r="C6" s="9" t="n"/>
@@ -799,15 +806,15 @@
       <c r="E6" s="9" t="n"/>
       <c r="F6" s="10" t="n"/>
     </row>
-    <row r="7" ht="48.5" customHeight="1">
+    <row r="7" ht="34" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>バックアップ（BAT-003）</t>
+          <t>会社休日の扱い</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>毎日 03:30 に pg_dump（プレーン SQL、--clean --if-exists、REPEATABLE READ の単一スナップショット）で DB 全体を backup/kintai_yyyyMMdd.sql へ出力し 7 世代を保持（KF-DD-BAT-003）。復元後は IDENTITY の採番値（シーケンス）が最大 id を超えていることを確認する。</t>
+          <t>年末年始（12/29〜1/3）は祝日と同じ表に『年末年始休暇（会社休日）』の名称で入れる。種別列は無く名称で区別する（課題 H-2）。KF-RD-002 の『種別（NATIONAL / COMPANY）を持たせる』は未実装。</t>
         </is>
       </c>
       <c r="C7" s="9" t="n"/>
@@ -815,15 +822,15 @@
       <c r="E7" s="9" t="n"/>
       <c r="F7" s="10" t="n"/>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="48.5" customHeight="1">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>マイグレーション</t>
+          <t>バックアップ（BAT-003）</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>現状は schema.sql（set_updated_at 関数・トリガを含む）の手動実行＋ spring.jpa.hibernate.ddl-auto=validate。列追加・索引追加は ALTER 文を別ファイルにし、将来 Flyway（V1__baseline.sql ＋ V2__… ）へ移行する（KF-DD-003 参照）。本書 3.4 の提案はこの方式で適用する。</t>
+          <t>毎日 03:30 に pg_dump（プレーン SQL、--clean --if-exists、REPEATABLE READ の単一スナップショット）で DB 全体を backup/kintai_yyyyMMdd.sql へ出力し 7 世代を保持（KF-DD-BAT-003）。復元後は IDENTITY の採番値（シーケンス）が最大 id を超えていることを確認する。なお BAT-001〜003 は設計のみで、現行の backend には実装が無い（@Scheduled・pg_dump 呼び出しなし）。</t>
         </is>
       </c>
       <c r="C8" s="9" t="n"/>
@@ -831,79 +838,64 @@
       <c r="E8" s="9" t="n"/>
       <c r="F8" s="10" t="n"/>
     </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+    <row r="9" ht="48.5" customHeight="1">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>マイグレーション</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Flyway（V1__init_schema.sql：set_updated_at 関数・トリガ・初期データを含む／V2・V3：祝日の初期データ／V4：attendance_breaks の追加／V5：requests への休憩・離席修正の 3 列と制約の追加）＋ spring.jpa.hibernate.ddl-auto=validate。V1〜V5 は適用後に編集せず、列追加・索引追加は次の版 V6__… のように新しいファイルで行う（KF-DD-003・KF-DD-006 参照）。本書 3.4 の提案はこの方式で適用する。</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="n"/>
+      <c r="D9" s="9" t="n"/>
+      <c r="E9" s="9" t="n"/>
+      <c r="F9" s="10" t="n"/>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>9.2 既知課題・未決事項（未解決のもの。解消済みは 9.2b）</t>
         </is>
       </c>
-      <c r="B10" s="9" t="n"/>
-      <c r="C10" s="9" t="n"/>
-      <c r="D10" s="9" t="n"/>
-      <c r="E10" s="9" t="n"/>
-      <c r="F10" s="10" t="n"/>
-    </row>
-    <row r="11" ht="19.5" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="9" t="n"/>
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="10" t="n"/>
+    </row>
+    <row r="12" ht="19.5" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>題名</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>影響</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>推奨対応</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>優先度</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="77.5" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>C-3</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>schema.sql の構成（開発用 DROP・DDL・初期データが 1 ファイルに同居）</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>先頭の DROP TABLE ... CASCADE（開発用）、DDL、トリガ／関数、初期データ（休暇種別 11 件・部署 3 件）が 1 ファイルに同居している。ヘッダは『PostgreSQL 18／KF-DD-003 v2.0』に修正済みで、旧『H2 / PostgreSQL 共通』の記述は解消。</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>本番 DB で誤実行すると全データを失う。</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>schema.sql を DDL 本体（DROP なし）／ dev-reset.sql（DROP）／ seed（初期データ）に分割。将来 Flyway（V1__baseline.sql）へ移行。</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>中</t>
         </is>
       </c>
     </row>
@@ -971,7 +963,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="63" customHeight="1">
+    <row r="15" ht="77.5" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
           <t>C-6</t>
@@ -984,7 +976,7 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>JST 固定は Hikari の connection-init-sql に依存する。psql での手動 SQL、マイグレーション実行、BAT-003 の pg_dump／復元、BI 接続は DB 既定の TimeZone（既定は UTC 等）で動く。</t>
+          <t>JST 固定は Hikari の connection-init-sql に依存する（Flyway はアプリの DataSource＝Hikari で実行するため JST）。psql での手動 SQL、BAT-003（設計）の pg_dump／復元、BI 接続は DB 既定の TimeZone（既定は UTC 等）で動く。</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
@@ -1035,7 +1027,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="34" customHeight="1">
+    <row r="17" ht="77.5" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
           <t>H-2</t>
@@ -1048,7 +1040,7 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>KF-DD-003 は「祝日・会社休日」だが種別列が無く name で区別する。</t>
+          <t>KF-DD-003 は「祝日・会社休日」だが種別列が無く name で区別する（V2 の年末年始は名称『年末年始休暇（会社休日）』）。KF-RD-002 §3.3 は種別（NATIONAL / COMPANY）を持たせる要件だが未実装。</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
@@ -1058,7 +1050,7 @@
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>kind 列（NATIONAL / COMPANY）追加を検討。</t>
+          <t>kind 列（NATIONAL / COMPANY）追加を検討（V6 以降のマイグレーションで追加。既存 64 件は名称から更新）。</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
@@ -1067,201 +1059,300 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+    <row r="18" ht="77.5" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>H-3</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>祝日の初期データが 2028 年末までで、以降は手動登録が必要</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>V2・V3 は 2026〜2028 年の 64 件のみ。2029 年以降は ONL-016 で登録する運用で、祝日の自動取り込み（内閣府 CSV。KF-RD-002 §3.3）は未実装。</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>2029 年の祝日・年始の会社休日（1/1〜1/3）を登録し忘れると、休暇申請の営業日数が過大に計算される（calcDays は土日と登録済みの祝日だけを除く）。新規構築した環境には ONL-016 の登録分が引き継がれない。</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>毎年 2 月頃に翌年分を ONL-016 で登録し、2028 年中に 2029 年分（特に 1/1〜1/3）を必ず登録する。新規環境用に同内容を V6 以降の INSERT … ON CONFLICT DO NOTHING としても追加する。10章の最終登録日確認を年次点検に含める。</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="92" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>H-4</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>V3（2028 年の祝日）の日付が推算値で、公表値と未照合</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>V3__seed_holidays_2028.sql の日付は祝日法の規則（春分・秋分は天文計算による推算）で求めたもので、内閣府の公表値（毎年 2 月頃に翌年分が公表）との照合は未実施。2028 年は振替休日・国民の休日が無い前提で、全 21 件（国民の祝日 16＋年末年始の会社休日 5）を登録している。</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>公表値と異なる日付（春分の日・秋分の日、制度改正など）が登録されたままだと、休暇申請の営業日数が 1 日ずれる。</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>公表後（2028 年分は 2027 年 2 月頃）に内閣府の一覧と照合し、差異があれば ONL-016 で修正するか、新しい版（V6 以降）で補正する。V3 は適用後に編集しない。</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>9.2b 解消済み（v2.0）の課題（履歴。この版で対応済み）</t>
         </is>
       </c>
-      <c r="B19" s="9" t="n"/>
-      <c r="C19" s="9" t="n"/>
-      <c r="D19" s="9" t="n"/>
-      <c r="E19" s="9" t="n"/>
-      <c r="F19" s="10" t="n"/>
-    </row>
-    <row r="20" ht="19.5" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="B21" s="9" t="n"/>
+      <c r="C21" s="9" t="n"/>
+      <c r="D21" s="9" t="n"/>
+      <c r="E21" s="9" t="n"/>
+      <c r="F21" s="10" t="n"/>
+    </row>
+    <row r="22" ht="19.5" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>題名</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>解消内容</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>根拠（DDL／規格）</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
         <is>
           <t>残る事項</t>
         </is>
       </c>
-      <c r="F20" s="6" t="inlineStr">
+      <c r="F22" s="6" t="inlineStr">
         <is>
           <t>状態</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="106.5" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
+    <row r="23" ht="106.5" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>C-1</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>updated_at が更新時に自動更新されない</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>全 9 表に BEFORE UPDATE FOR EACH ROW のトリガ trg_&lt;表&gt;_updated_at を追加し、共通関数 set_updated_at() が NEW.updated_at を CURRENT_TIMESTAMP にする。アプリは updated_at を SET しない（ONL-010〜012・019 の updated_at = ? は削除）。『未決（@PreUpdate か DB トリガ）』は DB トリガで決定。</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>V1 の全 9 表（V4 の attendance_breaks にも同様）に BEFORE UPDATE FOR EACH ROW のトリガ trg_&lt;表&gt;_updated_at を追加し、共通関数 set_updated_at() が NEW.updated_at を CURRENT_TIMESTAMP にする。アプリは updated_at を SET しない（ONL-010〜012・019 の updated_at = ? は削除）。『未決（@PreUpdate か DB トリガ）』は DB トリガで決定。</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>トリガは値が変わらない UPDATE でも、明示指定された updated_at があっても、トランザクション開始時刻で上書きする（仕様）。TimeZone の前提は課題 C-6。</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="F21" s="7" t="inlineStr">
+      <c r="F23" s="7" t="inlineStr">
         <is>
           <t>解消済み（v2.0）</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="92" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
+    <row r="24" ht="135.5" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>C-2</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>TIMESTAMP のタイムゾーン前提が DB 側で固定されていない（アプリ接続）</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>spring.datasource.hikari.connection-init-sql = SET TIME ZONE 'Asia/Tokyo' で全接続を JST にし、DEFAULT CURRENT_TIMESTAMP と updated_at トリガも JST の壁時計時刻になる。hibernate.jdbc.time_zone=Asia/Tokyo で Timestamp 変換も JST。</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>spring.datasource.hikari.connection-init-sql = SET TIME ZONE 'Asia/Tokyo' で全接続を JST にし、DEFAULT CURRENT_TIMESTAMP と updated_at トリガも JST の壁時計時刻になる。業務時刻は Clock（ClockConfig / AppTime。Asia/Tokyo 固定）から取得した LocalDateTime をそのまま保存する。hibernate.jdbc.time_zone は設定していない（application.properties に無い）。Docker では ENV TZ=Asia/Tokyo。</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>アプリ以外の接続は対象外（課題 C-6）。</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
+      <c r="E24" s="7" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr">
+      <c r="F24" s="7" t="inlineStr">
         <is>
           <t>解消済み（v2.0）</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+    <row r="25" ht="135.5" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>C-3</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>schema.sql の構成（開発用 DROP・DDL・初期データが 1 ファイルに同居）／手動実行</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>schema.sql を廃止し Flyway（backend/src/main/resources/db/migration/V1__init_schema.sql）へ移行。V1 は DROP を含まず、DDL・トリガ・初期データ（休暇種別 11 件・部署 5 件）を持つ。ユーザーは V1 に含めずアプリの初期化処理（DevDataInitializer / BootstrapAdminInitializer）が作る。開発用の全消去は backend/db/reset-dev.sql に分離。V1 は編集せず、変更は V2 以降を追加する。ddl-auto=validate を継続。</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>旧 schema.sql 由来の開発 DB は baseline-on-migrate で V1 適用済みとみなされ、V1 の追加列（users の 4 列）が入らない。reset-dev.sql で作り直す必要がある。</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>解消済み（v2.0）</t>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>9.3 ONL 規格が挙げた既知の制約・未対応（この表を使う処理の security 欄から抜粋）</t>
         </is>
       </c>
-      <c r="B24" s="9" t="n"/>
-      <c r="C24" s="9" t="n"/>
-      <c r="D24" s="9" t="n"/>
-      <c r="E24" s="9" t="n"/>
-      <c r="F24" s="10" t="n"/>
-    </row>
-    <row r="25" ht="19.5" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>処理ID</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>区分</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>内容（原文抜粋）</t>
-        </is>
-      </c>
-      <c r="D25" s="9" t="n"/>
-      <c r="E25" s="9" t="n"/>
-      <c r="F25" s="10" t="n"/>
-    </row>
-    <row r="26" ht="34" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>ONL-005</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>既知の制約</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>承認ルート確定後に上長が変更されても既存申請の approver_id は変わらない。管理者が1人のみで、その管理者自身が申請すると承認者がいなくなる（運用で別の管理者を用意する）。通知は type / request_id を持つため、画面は requestId があれば SCR-106 の該当申請へ遷移する（ONL-019）。</t>
-        </is>
-      </c>
-      <c r="D26" s="9" t="n"/>
-      <c r="E26" s="9" t="n"/>
-      <c r="F26" s="10" t="n"/>
-    </row>
-    <row r="27" ht="48.5" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>ONL-022</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>既知の制約</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>再提出で前回の承認履歴（差戻しコメントを含む）が削除される。下書きの内容を更新する API（PUT）は未定義のため、内容を直したい場合は新規申請になる（今後の課題）。上長が変更されていれば、再提出時の承認ルートは新しい上長で作り直される。管理者が 1 人のみで本人が申請者の場合は承認者がいなくなる（ONL-005 と同じ運用制約）。</t>
-        </is>
-      </c>
+      <c r="B27" s="9" t="n"/>
+      <c r="C27" s="9" t="n"/>
       <c r="D27" s="9" t="n"/>
       <c r="E27" s="9" t="n"/>
       <c r="F27" s="10" t="n"/>
     </row>
+    <row r="28" ht="19.5" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>処理ID</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>内容（原文抜粋）</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="n"/>
+      <c r="E28" s="9" t="n"/>
+      <c r="F28" s="10" t="n"/>
+    </row>
+    <row r="29" ht="34" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>ONL-005</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>既知の制約</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>承認ルート確定後に上長が変更されても既存申請の approver_id は変わらない。管理者が1人のみで、その管理者自身が申請すると承認者がいなくなる（運用で別の管理者を用意する）。通知は type / request_id を持つため、画面は requestId があれば SCR-106 の該当申請へ遷移する（ONL-019）。</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="n"/>
+      <c r="E29" s="9" t="n"/>
+      <c r="F29" s="10" t="n"/>
+    </row>
+    <row r="30" ht="48.5" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>ONL-022</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>既知の制約</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>再提出で前回の承認履歴（差戻しコメントを含む）が削除される。下書きの内容を更新する API（PUT）は未定義のため、内容を直したい場合は新規申請になる（今後の課題）。上長が変更されていれば、再提出時の承認ルートは新しい上長で作り直される。管理者が 1 人のみで本人が申請者の場合は承認者がいなくなる（ONL-005 と同じ運用制約）。</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="n"/>
+      <c r="E30" s="9" t="n"/>
+      <c r="F30" s="10" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="14">
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A11:F11"/>
     <mergeCell ref="B7:F7"/>
-    <mergeCell ref="A10:F10"/>
     <mergeCell ref="B6:F6"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="C26:F26"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B5:F5"/>
-    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C30:F30"/>
     <mergeCell ref="B8:F8"/>
-    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="C28:F28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -1275,7 +1366,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F12"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1286,6 +1377,7 @@
     <col width="10" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
@@ -1322,7 +1414,7 @@
       <c r="E3" s="9" t="n"/>
       <c r="F3" s="10" t="n"/>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="48.5" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
         <is>
           <t>1</t>
@@ -1340,13 +1432,13 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>当年・翌年分が登録済み（国民の祝日は年 16 日前後）</t>
+          <t>当年・翌年分が登録済み（国民の祝日は年 16 日前後）。V2・V3 適用直後は 2026 年 21 件・2027 年 22 件・2028 年 21 件（8章の例を実行した後は 2029 年 3 件）</t>
         </is>
       </c>
       <c r="E4" s="9" t="n"/>
       <c r="F4" s="10" t="n"/>
     </row>
-    <row r="5" ht="48.5" customHeight="1">
+    <row r="5" ht="34" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>2</t>
@@ -1354,17 +1446,17 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>翌年分の未登録チェック</t>
+          <t>V2・V3 初期データの欠落確認（2026〜2028 年は 64 件）</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>SELECT COUNT(*) FROM holidays WHERE holiday_date &gt;= date_trunc('year', CURRENT_DATE) + INTERVAL '1 year' AND holiday_date &lt; date_trunc('year', CURRENT_DATE) + INTERVAL '2 years';</t>
+          <t>SELECT COUNT(*) AS seed_range_rows FROM holidays WHERE holiday_date BETWEEN DATE '2026-01-01' AND DATE '2028-12-31';</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>1 以上（0 は登録漏れ）</t>
+          <t>64（ONL-016 で追加・削除した場合は増減する。V2・V3 の件数と一致しない場合は誤削除・誤登録の可能性）</t>
         </is>
       </c>
       <c r="E5" s="9" t="n"/>
@@ -1378,23 +1470,23 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>日付の重複</t>
+          <t>最終登録日（毎年の追加漏れの確認）</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>SELECT holiday_date, COUNT(*) FROM holidays GROUP BY 1 HAVING COUNT(*) &gt; 1;</t>
+          <t>SELECT MAX(holiday_date) AS last_registered FROM holidays;</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>0 行（uq_holidays_1）</t>
+          <t>V2・V3 適用直後は 2028-12-31。翌年 12 月 31 日以降であること（当年末が最終日のままなら翌年分が未登録）</t>
         </is>
       </c>
       <c r="E6" s="9" t="n"/>
       <c r="F6" s="10" t="n"/>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="48.5" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>4</t>
@@ -1402,23 +1494,23 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>範囲外の日付（課題 H-1）</t>
+          <t>年末年始の会社休日（12/29〜1/3）</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>SELECT id, holiday_date FROM holidays WHERE holiday_date NOT BETWEEN DATE '2000-01-01' AND DATE '2099-12-31';</t>
+          <t>SELECT holiday_date, name FROM holidays WHERE name LIKE '%会社休日%' ORDER BY holiday_date;</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>0 行（上記の異常系例を実行した場合は 1 行）</t>
+          <t>V2・V3 適用直後は 13 行（2026-12-29〜31、2027-01-02・03、2027-12-29〜31、2028-01-02・03、2028-12-29〜31）。翌年 1 月分が未登録なら追加する</t>
         </is>
       </c>
       <c r="E7" s="9" t="n"/>
       <c r="F7" s="10" t="n"/>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="48.5" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
           <t>5</t>
@@ -1426,23 +1518,23 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>土日に当たる登録（計算に影響しない冗長登録）</t>
+          <t>翌年分の未登録チェック</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>SELECT id, holiday_date, name FROM holidays WHERE EXTRACT(ISODOW FROM holiday_date) IN (6,7) ORDER BY holiday_date;</t>
+          <t>SELECT COUNT(*) FROM holidays WHERE holiday_date &gt;= date_trunc('year', CURRENT_DATE) + INTERVAL '1 year' AND holiday_date &lt; date_trunc('year', CURRENT_DATE) + INTERVAL '2 years';</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>運用判断（登録は可能。営業日計算では土日と重複するだけ）</t>
+          <t>1 以上（0 は登録漏れ）</t>
         </is>
       </c>
       <c r="E8" s="9" t="n"/>
       <c r="F8" s="10" t="n"/>
     </row>
-    <row r="9" ht="77.5" customHeight="1">
+    <row r="9" ht="34" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
           <t>6</t>
@@ -1450,23 +1542,23 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>祝日を含む申請の日数の妥当性（祝日が登録漏れだった可能性）</t>
+          <t>日付の重複</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>SELECT r.id, r.start_date, r.end_date, r.days FROM requests r WHERE r.request_type='LEAVE' AND r.unit='FULL' AND r.days &gt; (SELECT COUNT(*) FROM generate_series(r.start_date, r.end_date, INTERVAL '1 day') g(d) WHERE EXTRACT(ISODOW FROM g.d) &lt; 6 AND NOT EXISTS (SELECT 1 FROM holidays h WHERE h.holiday_date = g.d::date));</t>
+          <t>SELECT holiday_date, COUNT(*) FROM holidays GROUP BY 1 HAVING COUNT(*) &gt; 1;</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>0 行（現在の祝日マスタで再計算した営業日数より days が大きい申請。登録時点では祝日が未登録だった可能性）</t>
+          <t>0 行（uq_holidays_1）</t>
         </is>
       </c>
       <c r="E9" s="9" t="n"/>
       <c r="F9" s="10" t="n"/>
     </row>
-    <row r="10" ht="19.5" customHeight="1">
+    <row r="10" ht="34" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
           <t>7</t>
@@ -1474,17 +1566,17 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>名称の前後空白</t>
+          <t>範囲外の日付（課題 H-1）</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>SELECT id FROM holidays WHERE name &lt;&gt; BTRIM(name);</t>
+          <t>SELECT id, holiday_date FROM holidays WHERE holiday_date NOT BETWEEN DATE '2000-01-01' AND DATE '2099-12-31';</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>0 行</t>
+          <t>0 行（上記の異常系例を実行した場合は 1 行）</t>
         </is>
       </c>
       <c r="E10" s="9" t="n"/>
@@ -1498,46 +1590,121 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>updated_at トリガ trg_holidays_updated_at が存在し有効であること</t>
+          <t>土日に当たる登録（計算に影響しない冗長登録）</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>SELECT tgname, tgenabled FROM pg_trigger WHERE tgrelid = 'holidays'::regclass AND NOT tgisinternal;</t>
+          <t>SELECT id, holiday_date, name FROM holidays WHERE EXTRACT(ISODOW FROM holiday_date) IN (6,7) ORDER BY holiday_date;</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>1 行（trg_holidays_updated_at、tgenabled = 'O'＝有効）。0 行だと updated_at が更新されない</t>
+          <t>運用判断（登録は可能。営業日計算では土日と重複するだけ）</t>
         </is>
       </c>
       <c r="E11" s="9" t="n"/>
       <c r="F11" s="10" t="n"/>
     </row>
-    <row r="12" ht="19.5" customHeight="1">
+    <row r="12" ht="77.5" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>全 SQL を PostgreSQL 16 上で schema.sql（v2.0・トリガ含む）＋ 8章のデータに対して実行し、構文と期待結果（8章データでの結果）を確認済み。件数確認系は参照のみで更新しない。</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="n"/>
-      <c r="C12" s="9" t="n"/>
-      <c r="D12" s="9" t="n"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>祝日を含む申請の日数の妥当性（祝日が登録漏れだった可能性）</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>SELECT r.id, r.start_date, r.end_date, r.days FROM requests r WHERE r.request_type='LEAVE' AND r.unit='FULL' AND r.days &gt; (SELECT COUNT(*) FROM generate_series(r.start_date, r.end_date, INTERVAL '1 day') g(d) WHERE EXTRACT(ISODOW FROM g.d) &lt; 6 AND NOT EXISTS (SELECT 1 FROM holidays h WHERE h.holiday_date = g.d::date));</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>0 行（現在の祝日マスタで再計算した営業日数より days が大きい申請。登録時点では祝日が未登録だった可能性。V2 は 2026 年 1 月 2・3 日の会社休日を含まない）</t>
+        </is>
+      </c>
       <c r="E12" s="9" t="n"/>
       <c r="F12" s="10" t="n"/>
     </row>
+    <row r="13" ht="19.5" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>名称の前後空白</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>SELECT id FROM holidays WHERE name &lt;&gt; BTRIM(name);</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>0 行</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="n"/>
+      <c r="F13" s="10" t="n"/>
+    </row>
+    <row r="14" ht="34" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>updated_at トリガ trg_holidays_updated_at が存在し有効であること</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>SELECT tgname, tgenabled FROM pg_trigger WHERE tgrelid = 'holidays'::regclass AND NOT tgisinternal;</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>1 行（trg_holidays_updated_at、tgenabled = 'O'＝有効）。0 行だと updated_at が更新されない</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="n"/>
+      <c r="F14" s="10" t="n"/>
+    </row>
+    <row r="15" ht="19.5" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>全 SQL を PostgreSQL 16 上で V1〜V5 のマイグレーション（V1 は v2.0・トリガ含む）＋ 8章のデータに対して実行し、構文と期待結果（8章データでの結果）を確認済み。件数確認系は参照のみで更新しない。</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="n"/>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="9" t="n"/>
+      <c r="F15" s="10" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="14">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="D11:F11"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D14:F14"/>
     <mergeCell ref="D5:F5"/>
     <mergeCell ref="D4:F4"/>
+    <mergeCell ref="D12:F12"/>
     <mergeCell ref="D3:F3"/>
     <mergeCell ref="D9:F9"/>
-    <mergeCell ref="A12:F12"/>
     <mergeCell ref="D7:F7"/>
     <mergeCell ref="D8:F8"/>
     <mergeCell ref="D6:F6"/>
+    <mergeCell ref="A15:F15"/>
     <mergeCell ref="D10:F10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1552,7 +1719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1589,7 +1756,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="63" customHeight="1">
+    <row r="2" ht="68" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
           <t>1.0</t>
@@ -1611,6 +1778,52 @@
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr"/>
+    </row>
+    <row r="3" ht="98" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>V2__seed_holidays.sql（2026〜2027 年の国民の祝日＋年末年始の会社休日 43 件）を追加。初期データの出典・範囲・冪等性（ON CONFLICT (holiday_date) DO NOTHING）・毎年の追加運用（2028 年分は 2027 年中に ONL-016 または V3 で登録）を 1.1・8章・9.1・10章に記載。Repository のメソッド名を実コードに合わせて修正。課題 H-3 を追加。</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr"/>
+    </row>
+    <row r="4" ht="113" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>V3__seed_holidays_2028.sql（2028 年の国民の祝日 16 件＋年末年始の会社休日 5 件の計 21 件。ON CONFLICT (holiday_date) DO NOTHING。振替休日なし）を追加し、初期データを V2・V3 の 64 件（2026〜2028 年）に更新（1章・8章・9.1・10章）。次の追加は 2029 年分（2028 年中に ONL-016 または V6 以降）。V3 の日付は推算値で公表値と未照合のため課題 H-4 を追加し、課題 H-2・H-3 を更新。8章のデータ例を V2・V3 の id（1〜64）と 2029 年 1 月の先行登録例に変更。</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1625,7 +1838,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F31"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1636,6 +1849,7 @@
     <col width="30" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
@@ -1688,7 +1902,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>PostgreSQL 18 / UTF-8。DDL の正は backend/schema.sql。</t>
+          <t>PostgreSQL 18 / UTF-8。DDL の正は Flyway のマイグレーション（backend/src/main/resources/db/migration の V1__init_schema.sql）。</t>
         </is>
       </c>
       <c r="C5" s="9" t="n"/>
@@ -1704,7 +1918,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>想定件数/年：〜20（国民の祝日 約 16 日＋会社休日）</t>
+          <t>想定件数/年：〜20（国民の祝日 約 16 日＋会社休日）。V2・V3 の初期データは 2026 年 21 件・2027 年 22 件・2028 年 21 件の計 64 件</t>
         </is>
       </c>
       <c r="C6" s="9" t="n"/>
@@ -1808,15 +2022,15 @@
       <c r="E12" s="9" t="n"/>
       <c r="F12" s="10" t="n"/>
     </row>
-    <row r="13" ht="19.5" customHeight="1">
+    <row r="13" ht="92" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>Entity クラス</t>
+          <t>初期データ</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>com.example.kintaiflow.entity.Holiday</t>
+          <t>V2__seed_holidays.sql（2026-01-01〜2027-12-31 の 43 件）と V3__seed_holidays_2028.sql（2028 年 21 件）が投入する（合計 64 件。id は適用順に 1〜64）。出典は国民の祝日（振替休日・国民の休日を含む。2026 年 18 件・2027 年 17 件・2028 年 16 件）と、年末年始を会社休日として登録したもの（KF-RD-002。2026 年 3 件〔12/29〜31〕・2027 年 5 件〔1/2・1/3・12/29〜31〕・2028 年 5 件〔1/2・1/3・12/29〜31〕、名称は『年末年始休暇（会社休日）』）。INSERT は ON CONFLICT (holiday_date) DO NOTHING で、同じ日付が既にあれば何もしない（冪等。ONL-016 で先に登録済みの行は名称も含め変更しない）。V3 は 2028 年に振替休日が無いことを前提とし、日付は推算値で内閣府の公表値との照合は未実施（課題 H-4）。2029 年 1 月の元日・年始の会社休日（1/1〜1/3）と 2029 年以降は含まない。以降の年は ONL-016 または V6 以降のマイグレーションで追加する（9.1）。2026-01-02・01-03 は含まない。</t>
         </is>
       </c>
       <c r="C13" s="9" t="n"/>
@@ -1827,12 +2041,12 @@
     <row r="14" ht="19.5" customHeight="1">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>Repository</t>
+          <t>Entity クラス</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>repository.HolidayRepository（findByHolidayDateBetween / existsByHolidayDate / deleteById ほか）</t>
+          <t>com.example.kintaiflow.entity.Holiday</t>
         </is>
       </c>
       <c r="C14" s="9" t="n"/>
@@ -1840,89 +2054,82 @@
       <c r="E14" s="9" t="n"/>
       <c r="F14" s="10" t="n"/>
     </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+    <row r="15" ht="19.5" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>Repository</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>repository.HolidayRepository（findByHolidayDateBetweenOrderByHolidayDate / existsByHolidayDate / deleteHolidayById）</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="9" t="n"/>
+      <c r="F15" s="10" t="n"/>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>1.2 主な利用処理（オンライン処理・バッチ）</t>
         </is>
       </c>
-      <c r="B16" s="9" t="n"/>
-      <c r="C16" s="9" t="n"/>
-      <c r="D16" s="9" t="n"/>
-      <c r="E16" s="9" t="n"/>
-      <c r="F16" s="10" t="n"/>
-    </row>
-    <row r="17" ht="19.5" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="9" t="n"/>
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="9" t="n"/>
+      <c r="F17" s="10" t="n"/>
+    </row>
+    <row r="18" ht="19.5" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>処理ID</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>処理名</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>API / 種別</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>CRUD</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
         <is>
           <t>備考（規格 tables の注記ほか）</t>
         </is>
       </c>
-      <c r="F17" s="10" t="n"/>
-    </row>
-    <row r="18" ht="19.5" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="F18" s="10" t="n"/>
+    </row>
+    <row r="19" ht="19.5" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>ONL-005</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>申請作成</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>API-005 POST /api/requests</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>R</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr"/>
-      <c r="F18" s="10" t="n"/>
-    </row>
-    <row r="19" ht="34" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>ONL-016</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>祝日管理</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>API-016 GET / POST / DELETE /api/admin/holidays[/{id}]</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>C/R/D</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr"/>
@@ -1931,22 +2138,22 @@
     <row r="20" ht="34" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>ONL-022</t>
+          <t>ONL-016</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>申請提出</t>
+          <t>祝日管理</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>API-022 POST /api/requests/{id}/submit</t>
+          <t>API-016 GET / POST / DELETE /api/admin/holidays[/{id}]</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>C/R/D</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr"/>
@@ -1955,77 +2162,82 @@
     <row r="21" ht="34" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
         <is>
+          <t>ONL-022</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>申請提出</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>API-022 POST /api/requests/{id}/submit</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr"/>
+      <c r="F21" s="10" t="n"/>
+    </row>
+    <row r="22" ht="34" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
           <t>BAT-003</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>データバックアップ（pg_dump）</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>バッチ</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>pg_dump による全表読取（アプリ SQL なし）</t>
         </is>
       </c>
-      <c r="F21" s="10" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="F22" s="10" t="n"/>
+    </row>
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>1.3 関連設計書</t>
         </is>
       </c>
-      <c r="B23" s="9" t="n"/>
-      <c r="C23" s="9" t="n"/>
-      <c r="D23" s="9" t="n"/>
-      <c r="E23" s="9" t="n"/>
-      <c r="F23" s="10" t="n"/>
-    </row>
-    <row r="24" ht="19.5" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>文書番号</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>文書名</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>関連内容</t>
-        </is>
-      </c>
+      <c r="B24" s="9" t="n"/>
+      <c r="C24" s="9" t="n"/>
       <c r="D24" s="9" t="n"/>
       <c r="E24" s="9" t="n"/>
       <c r="F24" s="10" t="n"/>
     </row>
     <row r="25" ht="19.5" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>KF-DD-003</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>テーブル設計書（総覧）</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>ER 図・CRUD マトリクス・命名規約・型方針・マイグレーション方針</t>
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>文書番号</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>文書名</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>関連内容</t>
         </is>
       </c>
       <c r="D25" s="9" t="n"/>
@@ -2035,17 +2247,17 @@
     <row r="26" ht="19.5" customHeight="1">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>KF-BD-003</t>
+          <t>KF-DD-003</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>テーブル定義書（基本）</t>
+          <t>テーブル設計書（総覧）</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>論理名・基本項目</t>
+          <t>ER 図・CRUD マトリクス・命名規約・型方針・マイグレーション方針</t>
         </is>
       </c>
       <c r="D26" s="9" t="n"/>
@@ -2055,17 +2267,17 @@
     <row r="27" ht="19.5" customHeight="1">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>KF-BD-005</t>
+          <t>KF-BD-003</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>コード定義書</t>
+          <t>テーブル定義書（基本）</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>コード値と状態遷移の基本設計</t>
+          <t>論理名・基本項目</t>
         </is>
       </c>
       <c r="D27" s="9" t="n"/>
@@ -2075,17 +2287,17 @@
     <row r="28" ht="19.5" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>KF-DD-001</t>
+          <t>KF-BD-005</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>オンライン設計書</t>
+          <t>コード定義書</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>ONL-001〜022 の概要</t>
+          <t>コード値と状態遷移の基本設計</t>
         </is>
       </c>
       <c r="D28" s="9" t="n"/>
@@ -2095,17 +2307,17 @@
     <row r="29" ht="19.5" customHeight="1">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>KF-DD-ONL-xxx</t>
+          <t>KF-DD-001</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>オンライン詳細設計書</t>
+          <t>オンライン設計書</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>アクセスパターンの根拠（SQL・排他）</t>
+          <t>ONL-001〜022 の概要（ONL-023 以降は個別のオンライン詳細設計書）</t>
         </is>
       </c>
       <c r="D29" s="9" t="n"/>
@@ -2115,17 +2327,17 @@
     <row r="30" ht="19.5" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>KF-DD-004 / BAT</t>
+          <t>KF-DD-ONL-xxx</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>バッチ設計書</t>
+          <t>オンライン詳細設計書</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>BAT-001〜003 の使用</t>
+          <t>アクセスパターンの根拠（SQL・排他）</t>
         </is>
       </c>
       <c r="D30" s="9" t="n"/>
@@ -2135,50 +2347,71 @@
     <row r="31" ht="19.5" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>backend/schema.sql</t>
+          <t>KF-DD-004 / BAT</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>DDL 本体</t>
+          <t>バッチ設計書</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>本書の自動生成元</t>
+          <t>BAT-001〜003 の使用</t>
         </is>
       </c>
       <c r="D31" s="9" t="n"/>
       <c r="E31" s="9" t="n"/>
       <c r="F31" s="10" t="n"/>
     </row>
+    <row r="32" ht="106.5" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>backend/src/main/resources/db/migration/V1__init_schema.sql・V4__attendance_breaks.sql・V5__break_correction_request.sql</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>DDL 本体</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>本書の自動生成元（V2・V3 は祝日の初期データのみ）</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="n"/>
+      <c r="E32" s="9" t="n"/>
+      <c r="F32" s="10" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="28">
+  <mergeCells count="29">
     <mergeCell ref="B4:F4"/>
-    <mergeCell ref="A16:F16"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="B3:F3"/>
-    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="C32:F32"/>
     <mergeCell ref="C28:F28"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="E20:F20"/>
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="E19:F19"/>
-    <mergeCell ref="A23:F23"/>
     <mergeCell ref="C30:F30"/>
+    <mergeCell ref="A17:F17"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B8:F8"/>
-    <mergeCell ref="C24:F24"/>
     <mergeCell ref="B13:F13"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="C26:F26"/>
     <mergeCell ref="C29:F29"/>
     <mergeCell ref="C25:F25"/>
     <mergeCell ref="B9:F9"/>
+    <mergeCell ref="A24:F24"/>
     <mergeCell ref="C31:F31"/>
     <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B15:F15"/>
     <mergeCell ref="B5:F5"/>
+    <mergeCell ref="E22:F22"/>
     <mergeCell ref="C27:F27"/>
     <mergeCell ref="E18:F18"/>
     <mergeCell ref="E21:F21"/>
@@ -2195,7 +2428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:M9"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2213,10 +2446,11 @@
     <col width="40" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>2.1 列定義（schema.sql から自動生成）</t>
+          <t>2.1 列定義（db/migration の V1・V4・V5 から自動生成。物理列順）</t>
         </is>
       </c>
       <c r="B2" s="9" t="n"/>
@@ -2361,7 +2595,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="63" customHeight="1">
       <c r="A5" s="7" t="n">
         <v>2</v>
       </c>
@@ -2408,7 +2642,7 @@
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>ONL-016 の登録（2000-01-01〜2099-12-31 の実在日付、土日も可）。一意。</t>
+          <t>ONL-016 の登録（2000-01-01〜2099-12-31 の実在日付、土日も可）。初期データは V2（2026〜2027 年）・V3（2028 年）の INSERT。一意。</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr">
@@ -2593,7 +2827,7 @@
     <row r="9" ht="34" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>キー：PK=主キー／FK=外部キー／UQ=単一列 UNIQUE／UQ*=複合 UNIQUE の構成列。型・桁・NULL・既定値は schema.sql の定義。『使用ONL』は ONL 規格の mapping で『○』（その処理で使用）とされたもの。「DB の DEFAULT」はアプリが値を指定せず DB が設定する（Entity は insertable=false, updatable=false）。</t>
+          <t>キー：PK=主キー／FK=外部キー／UQ=単一列 UNIQUE／UQ*=複合 UNIQUE の構成列。型・桁・NULL・既定値はマイグレーション（V1・V4・V5）の定義。『使用ONL』は ONL 規格の mapping で『○』（その処理で使用）とされたもの。「DB の DEFAULT」はアプリが値を指定せず DB が設定する（Entity は insertable=false, updatable=false）。</t>
         </is>
       </c>
       <c r="B9" s="9" t="n"/>
@@ -2626,7 +2860,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F23"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2637,10 +2871,11 @@
     <col width="50" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>3.1 制約一覧（schema.sql の定義名のまま）</t>
+          <t>3.1 制約一覧（マイグレーションの定義名のまま）</t>
         </is>
       </c>
       <c r="B2" s="9" t="n"/>
@@ -2817,6 +3052,7 @@
       </c>
       <c r="F8" s="10" t="n"/>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
@@ -2928,6 +3164,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
@@ -3004,10 +3241,11 @@
       <c r="E19" s="9" t="n"/>
       <c r="F19" s="10" t="n"/>
     </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>3.4 推奨する変更（schema.sql は変更しない。提案のみ。DDL は schema.sql＋8章データに対して実行確認済み）</t>
+          <t>3.4 推奨する変更（適用済みのマイグレーションは変更しない。提案のみ。DDL は V1〜V5＋8章データに対して実行確認済み）</t>
         </is>
       </c>
       <c r="B21" s="9" t="n"/>
@@ -3095,7 +3333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F16"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3106,6 +3344,7 @@
     <col width="40" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
@@ -3162,6 +3401,7 @@
       <c r="E4" s="7" t="inlineStr"/>
       <c r="F4" s="7" t="inlineStr"/>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
@@ -3218,6 +3458,7 @@
       <c r="E8" s="7" t="inlineStr"/>
       <c r="F8" s="7" t="inlineStr"/>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
@@ -3246,6 +3487,7 @@
       <c r="E11" s="9" t="n"/>
       <c r="F11" s="10" t="n"/>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
@@ -3329,7 +3571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:J18"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3344,6 +3586,7 @@
     <col width="26" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
@@ -3500,6 +3743,7 @@
       <c r="I7" s="9" t="n"/>
       <c r="J7" s="10" t="n"/>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
@@ -3943,7 +4187,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F15"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3954,6 +4198,7 @@
     <col width="40" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
@@ -4030,6 +4275,7 @@
       <c r="E6" s="9" t="n"/>
       <c r="F6" s="10" t="n"/>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
@@ -4082,6 +4328,7 @@
       <c r="E10" s="9" t="n"/>
       <c r="F10" s="10" t="n"/>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
@@ -4118,7 +4365,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>users → requests → approval_steps → leave_balances / attendance_records → notifications の一方向。逆順で取得しない（ONL-005/008/010〜013/017 の規格で統一）。</t>
+          <t>users → requests → approval_steps → leave_balances / attendance_records → attendance_breaks → notifications の一方向。逆順で取得しない（ONL-005/008/010〜013/017 の規格で統一。休憩・離席の打刻 ONL-024/025 は attendance_records の行ロック → attendance_breaks）。</t>
         </is>
       </c>
       <c r="C14" s="9" t="n"/>
@@ -4169,7 +4416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:K25"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4185,6 +4432,7 @@
     <col width="22" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
@@ -4210,8 +4458,8 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>2026 年の祝日の一部（会社休日の例を含む）。
-例の INSERT は schema.sql 実行直後の DB に、表の依存順（departments → leave_types → users → leave_balances → attendance_records → requests → approval_steps → holidays → notifications）で実行できる。外部キーは SELECT で解決しているため id の採番値に依存しない。PostgreSQL 16 で実行確認済み。</t>
+          <t>V2・V3 の初期データ 64 件（2026〜2028 年。id は適用順の 1〜64）と、その後に ONL-016 で 2029 年 1 月の年始分を先行登録した例（id 65〜67）。
+例の INSERT は V1〜V5 適用直後の DB（開発用シードを入れていない状態）に、表の依存順（departments → leave_types → users → leave_balances → attendance_records → attendance_breaks → requests → approval_steps → holidays → notifications）で実行できる。外部キーは SELECT で解決しているため id の採番値に依存しない。PostgreSQL 16 で実行確認済み。</t>
         </is>
       </c>
       <c r="C3" s="9" t="n"/>
@@ -4224,6 +4472,7 @@
       <c r="J3" s="9" t="n"/>
       <c r="K3" s="10" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
@@ -4274,12 +4523,12 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>文化の日</t>
+          <t>元日（V2）</t>
         </is>
       </c>
       <c r="D7" s="9" t="n"/>
@@ -4294,17 +4543,17 @@
     <row r="8" ht="19.5" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>…</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>…</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>勤労感謝の日</t>
+          <t>…（V2 の 43 件。2026 年は 1〜21、2027 年は 22〜43）</t>
         </is>
       </c>
       <c r="D8" s="9" t="n"/>
@@ -4319,17 +4568,17 @@
     <row r="9" ht="19.5" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>年末休業（会社休日）</t>
+          <t>文化の日（V2）</t>
         </is>
       </c>
       <c r="D9" s="9" t="n"/>
@@ -4341,14 +4590,47 @@
       <c r="J9" s="9" t="n"/>
       <c r="K9" s="10" t="n"/>
     </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>8.3 INSERT 例（実際に実行できる SQL）</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="n"/>
-      <c r="C11" s="9" t="n"/>
+    <row r="10" ht="19.5" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>2026-12-29</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>年末年始休暇（会社休日）（V2）</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="n"/>
+      <c r="E10" s="9" t="n"/>
+      <c r="F10" s="9" t="n"/>
+      <c r="G10" s="9" t="n"/>
+      <c r="H10" s="9" t="n"/>
+      <c r="I10" s="9" t="n"/>
+      <c r="J10" s="9" t="n"/>
+      <c r="K10" s="10" t="n"/>
+    </row>
+    <row r="11" ht="19.5" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>2027-01-02</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>年末年始休暇（会社休日）（V2）</t>
+        </is>
+      </c>
       <c r="D11" s="9" t="n"/>
       <c r="E11" s="9" t="n"/>
       <c r="F11" s="9" t="n"/>
@@ -4359,17 +4641,21 @@
       <c r="K11" s="10" t="n"/>
     </row>
     <row r="12" ht="19.5" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>SQL</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="n"/>
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>2027-03-22</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>休日（春分の日の振替休日）（V2）</t>
+        </is>
+      </c>
       <c r="D12" s="9" t="n"/>
       <c r="E12" s="9" t="n"/>
       <c r="F12" s="9" t="n"/>
@@ -4382,15 +4668,19 @@
     <row r="13" ht="19.5" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>INSERT INTO holidays(holiday_date,name) VALUES (DATE '2026-11-03','文化の日');</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="n"/>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>2027-12-31</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>年末年始休暇（会社休日）（V2）</t>
+        </is>
+      </c>
       <c r="D13" s="9" t="n"/>
       <c r="E13" s="9" t="n"/>
       <c r="F13" s="9" t="n"/>
@@ -4403,15 +4693,19 @@
     <row r="14" ht="19.5" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>INSERT INTO holidays(holiday_date,name) VALUES (DATE '2026-11-23','勤労感謝の日');</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="n"/>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>2028-01-01</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>元日（V3）</t>
+        </is>
+      </c>
       <c r="D14" s="9" t="n"/>
       <c r="E14" s="9" t="n"/>
       <c r="F14" s="9" t="n"/>
@@ -4424,15 +4718,19 @@
     <row r="15" ht="19.5" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B15" s="12" t="inlineStr">
-        <is>
-          <t>INSERT INTO holidays(holiday_date,name) VALUES (DATE '2026-12-29','年末休業（会社休日）');</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="n"/>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>…（V3 の 21 件。2028 年は 44〜64。振替休日は無い）</t>
+        </is>
+      </c>
       <c r="D15" s="9" t="n"/>
       <c r="E15" s="9" t="n"/>
       <c r="F15" s="9" t="n"/>
@@ -4442,14 +4740,47 @@
       <c r="J15" s="9" t="n"/>
       <c r="K15" s="10" t="n"/>
     </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>8.4 異常系の例（制約で拒否される INSERT。実行確認済み）</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="n"/>
-      <c r="C17" s="9" t="n"/>
+    <row r="16" ht="19.5" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>2028-12-31</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>年末年始休暇（会社休日）（V3）</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="n"/>
+      <c r="E16" s="9" t="n"/>
+      <c r="F16" s="9" t="n"/>
+      <c r="G16" s="9" t="n"/>
+      <c r="H16" s="9" t="n"/>
+      <c r="I16" s="9" t="n"/>
+      <c r="J16" s="9" t="n"/>
+      <c r="K16" s="10" t="n"/>
+    </row>
+    <row r="17" ht="19.5" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>2029-01-01</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>元日（上記 INSERT の例）</t>
+        </is>
+      </c>
       <c r="D17" s="9" t="n"/>
       <c r="E17" s="9" t="n"/>
       <c r="F17" s="9" t="n"/>
@@ -4460,128 +4791,105 @@
       <c r="K17" s="10" t="n"/>
     </row>
     <row r="18" ht="19.5" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>ケース</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>SQL</t>
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>2029-01-02</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>年末年始休暇（会社休日）（同上）</t>
         </is>
       </c>
       <c r="D18" s="9" t="n"/>
       <c r="E18" s="9" t="n"/>
       <c r="F18" s="9" t="n"/>
       <c r="G18" s="9" t="n"/>
-      <c r="H18" s="10" t="n"/>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>結果（SQLSTATE）</t>
-        </is>
-      </c>
+      <c r="H18" s="9" t="n"/>
+      <c r="I18" s="9" t="n"/>
       <c r="J18" s="9" t="n"/>
       <c r="K18" s="10" t="n"/>
     </row>
-    <row r="19" ht="34" customHeight="1">
+    <row r="19" ht="19.5" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>67</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>日付重複（uq_holidays_1）</t>
-        </is>
-      </c>
-      <c r="C19" s="12" t="inlineStr">
-        <is>
-          <t>INSERT INTO holidays(holiday_date,name) VALUES (DATE '2026-11-03','重複');</t>
+          <t>2029-01-03</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>年末年始休暇（会社休日）（同上）</t>
         </is>
       </c>
       <c r="D19" s="9" t="n"/>
       <c r="E19" s="9" t="n"/>
       <c r="F19" s="9" t="n"/>
       <c r="G19" s="9" t="n"/>
-      <c r="H19" s="10" t="n"/>
-      <c r="I19" s="7" t="inlineStr">
-        <is>
-          <t>23505 一意制約違反</t>
-        </is>
-      </c>
+      <c r="H19" s="9" t="n"/>
+      <c r="I19" s="9" t="n"/>
       <c r="J19" s="9" t="n"/>
       <c r="K19" s="10" t="n"/>
     </row>
-    <row r="20" ht="19.5" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>name が NULL</t>
-        </is>
-      </c>
-      <c r="C20" s="12" t="inlineStr">
-        <is>
-          <t>INSERT INTO holidays(holiday_date,name) VALUES (DATE '2026-12-30',NULL);</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="n"/>
-      <c r="E20" s="9" t="n"/>
-      <c r="F20" s="9" t="n"/>
-      <c r="G20" s="9" t="n"/>
-      <c r="H20" s="10" t="n"/>
-      <c r="I20" s="7" t="inlineStr">
-        <is>
-          <t>23502 NOT NULL 違反</t>
-        </is>
-      </c>
-      <c r="J20" s="9" t="n"/>
-      <c r="K20" s="10" t="n"/>
-    </row>
-    <row r="21" ht="48.5" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>範囲外の日付（現状は DB が止めない。課題 H-1）</t>
-        </is>
-      </c>
-      <c r="C21" s="12" t="inlineStr">
-        <is>
-          <t>INSERT INTO holidays(holiday_date,name) VALUES (DATE '1999-01-01','範囲外');</t>
-        </is>
-      </c>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>8.3 INSERT 例（実際に実行できる SQL）</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="n"/>
+      <c r="C21" s="9" t="n"/>
       <c r="D21" s="9" t="n"/>
       <c r="E21" s="9" t="n"/>
       <c r="F21" s="9" t="n"/>
       <c r="G21" s="9" t="n"/>
-      <c r="H21" s="10" t="n"/>
-      <c r="I21" s="7" t="inlineStr">
-        <is>
-          <t>成功してしまう（DB は拒否しない＝課題。実行した場合は DELETE で元に戻すこと）</t>
-        </is>
-      </c>
+      <c r="H21" s="9" t="n"/>
+      <c r="I21" s="9" t="n"/>
       <c r="J21" s="9" t="n"/>
       <c r="K21" s="10" t="n"/>
     </row>
-    <row r="23">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>8.5 updated_at 自動更新トリガの動作確認（UPDATE で updated_at が created_at より後になる）</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="n"/>
+    <row r="22" ht="19.5" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="n"/>
+      <c r="D22" s="9" t="n"/>
+      <c r="E22" s="9" t="n"/>
+      <c r="F22" s="9" t="n"/>
+      <c r="G22" s="9" t="n"/>
+      <c r="H22" s="9" t="n"/>
+      <c r="I22" s="9" t="n"/>
+      <c r="J22" s="9" t="n"/>
+      <c r="K22" s="10" t="n"/>
+    </row>
+    <row r="23" ht="19.5" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>INSERT INTO holidays(holiday_date,name) VALUES (DATE '2029-01-01','元日');</t>
+        </is>
+      </c>
       <c r="C23" s="9" t="n"/>
       <c r="D23" s="9" t="n"/>
       <c r="E23" s="9" t="n"/>
@@ -4593,14 +4901,14 @@
       <c r="K23" s="10" t="n"/>
     </row>
     <row r="24" ht="19.5" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>SQL（値は変更しない UPDATE。トリガにより updated_at のみ更新される）</t>
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>INSERT INTO holidays(holiday_date,name) VALUES (DATE '2029-01-02','年末年始休暇（会社休日）');</t>
         </is>
       </c>
       <c r="C24" s="9" t="n"/>
@@ -4608,24 +4916,20 @@
       <c r="E24" s="9" t="n"/>
       <c r="F24" s="9" t="n"/>
       <c r="G24" s="9" t="n"/>
-      <c r="H24" s="10" t="n"/>
-      <c r="I24" s="6" t="inlineStr">
-        <is>
-          <t>期待結果</t>
-        </is>
-      </c>
+      <c r="H24" s="9" t="n"/>
+      <c r="I24" s="9" t="n"/>
       <c r="J24" s="9" t="n"/>
       <c r="K24" s="10" t="n"/>
     </row>
-    <row r="25" ht="34" customHeight="1">
+    <row r="25" ht="19.5" customHeight="1">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>WITH u AS (UPDATE holidays SET name = name WHERE id = (SELECT MIN(id) FROM holidays) RETURNING created_at, updated_at) SELECT updated_at &gt; created_at AS trigger_worked FROM u;</t>
+          <t>INSERT INTO holidays(holiday_date,name) VALUES (DATE '2029-01-03','年末年始休暇（会社休日）');</t>
         </is>
       </c>
       <c r="C25" s="9" t="n"/>
@@ -4633,43 +4937,251 @@
       <c r="E25" s="9" t="n"/>
       <c r="F25" s="9" t="n"/>
       <c r="G25" s="9" t="n"/>
-      <c r="H25" s="10" t="n"/>
-      <c r="I25" s="7" t="inlineStr">
-        <is>
-          <t>trigger_worked = true（8章のデータを投入済みの DB で、INSERT と別トランザクションの場合）</t>
-        </is>
-      </c>
+      <c r="H25" s="9" t="n"/>
+      <c r="I25" s="9" t="n"/>
       <c r="J25" s="9" t="n"/>
       <c r="K25" s="10" t="n"/>
     </row>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>8.4 異常系の例（制約で拒否される INSERT。実行確認済み）</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="n"/>
+      <c r="C27" s="9" t="n"/>
+      <c r="D27" s="9" t="n"/>
+      <c r="E27" s="9" t="n"/>
+      <c r="F27" s="9" t="n"/>
+      <c r="G27" s="9" t="n"/>
+      <c r="H27" s="9" t="n"/>
+      <c r="I27" s="9" t="n"/>
+      <c r="J27" s="9" t="n"/>
+      <c r="K27" s="10" t="n"/>
+    </row>
+    <row r="28" ht="19.5" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>ケース</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="n"/>
+      <c r="E28" s="9" t="n"/>
+      <c r="F28" s="9" t="n"/>
+      <c r="G28" s="9" t="n"/>
+      <c r="H28" s="10" t="n"/>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>結果（SQLSTATE）</t>
+        </is>
+      </c>
+      <c r="J28" s="9" t="n"/>
+      <c r="K28" s="10" t="n"/>
+    </row>
+    <row r="29" ht="34" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>日付重複（uq_holidays_1）</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>INSERT INTO holidays(holiday_date,name) VALUES (DATE '2026-11-03','重複');</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="n"/>
+      <c r="E29" s="9" t="n"/>
+      <c r="F29" s="9" t="n"/>
+      <c r="G29" s="9" t="n"/>
+      <c r="H29" s="10" t="n"/>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>23505 一意制約違反</t>
+        </is>
+      </c>
+      <c r="J29" s="9" t="n"/>
+      <c r="K29" s="10" t="n"/>
+    </row>
+    <row r="30" ht="19.5" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>name が NULL</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>INSERT INTO holidays(holiday_date,name) VALUES (DATE '2029-02-11',NULL);</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="n"/>
+      <c r="E30" s="9" t="n"/>
+      <c r="F30" s="9" t="n"/>
+      <c r="G30" s="9" t="n"/>
+      <c r="H30" s="10" t="n"/>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>23502 NOT NULL 違反</t>
+        </is>
+      </c>
+      <c r="J30" s="9" t="n"/>
+      <c r="K30" s="10" t="n"/>
+    </row>
+    <row r="31" ht="48.5" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>範囲外の日付（現状は DB が止めない。課題 H-1）</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>INSERT INTO holidays(holiday_date,name) VALUES (DATE '1999-01-01','範囲外');</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="n"/>
+      <c r="E31" s="9" t="n"/>
+      <c r="F31" s="9" t="n"/>
+      <c r="G31" s="9" t="n"/>
+      <c r="H31" s="10" t="n"/>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>成功してしまう（DB は拒否しない＝課題。実行した場合は DELETE で元に戻すこと）</t>
+        </is>
+      </c>
+      <c r="J31" s="9" t="n"/>
+      <c r="K31" s="10" t="n"/>
+    </row>
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>8.5 updated_at 自動更新トリガの動作確認（UPDATE で updated_at が created_at より後になる）</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="n"/>
+      <c r="C33" s="9" t="n"/>
+      <c r="D33" s="9" t="n"/>
+      <c r="E33" s="9" t="n"/>
+      <c r="F33" s="9" t="n"/>
+      <c r="G33" s="9" t="n"/>
+      <c r="H33" s="9" t="n"/>
+      <c r="I33" s="9" t="n"/>
+      <c r="J33" s="9" t="n"/>
+      <c r="K33" s="10" t="n"/>
+    </row>
+    <row r="34" ht="19.5" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>SQL（値は変更しない UPDATE。トリガにより updated_at のみ更新される）</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="n"/>
+      <c r="D34" s="9" t="n"/>
+      <c r="E34" s="9" t="n"/>
+      <c r="F34" s="9" t="n"/>
+      <c r="G34" s="9" t="n"/>
+      <c r="H34" s="10" t="n"/>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="J34" s="9" t="n"/>
+      <c r="K34" s="10" t="n"/>
+    </row>
+    <row r="35" ht="34" customHeight="1">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>WITH u AS (UPDATE holidays SET name = name WHERE id = (SELECT MIN(id) FROM holidays) RETURNING created_at, updated_at) SELECT updated_at &gt; created_at AS trigger_worked FROM u;</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="n"/>
+      <c r="D35" s="9" t="n"/>
+      <c r="E35" s="9" t="n"/>
+      <c r="F35" s="9" t="n"/>
+      <c r="G35" s="9" t="n"/>
+      <c r="H35" s="10" t="n"/>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>trigger_worked = true（8章のデータを投入済みの DB で、INSERT と別トランザクションの場合）</t>
+        </is>
+      </c>
+      <c r="J35" s="9" t="n"/>
+      <c r="K35" s="10" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="26">
+  <mergeCells count="36">
+    <mergeCell ref="C16:K16"/>
+    <mergeCell ref="C10:K10"/>
+    <mergeCell ref="I28:K28"/>
+    <mergeCell ref="C31:H31"/>
     <mergeCell ref="C9:K9"/>
-    <mergeCell ref="A11:K11"/>
-    <mergeCell ref="B15:K15"/>
-    <mergeCell ref="B24:H24"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="C21:H21"/>
-    <mergeCell ref="I24:K24"/>
+    <mergeCell ref="B24:K24"/>
+    <mergeCell ref="C12:K12"/>
+    <mergeCell ref="C11:K11"/>
+    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="C17:K17"/>
+    <mergeCell ref="B25:K25"/>
+    <mergeCell ref="I35:K35"/>
     <mergeCell ref="C8:K8"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="B25:H25"/>
+    <mergeCell ref="I29:K29"/>
     <mergeCell ref="B3:K3"/>
+    <mergeCell ref="A27:K27"/>
     <mergeCell ref="C7:K7"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="C19:H19"/>
+    <mergeCell ref="B22:K22"/>
+    <mergeCell ref="C19:K19"/>
+    <mergeCell ref="A21:K21"/>
+    <mergeCell ref="C28:H28"/>
+    <mergeCell ref="C13:K13"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="B12:K12"/>
-    <mergeCell ref="C18:H18"/>
+    <mergeCell ref="C18:K18"/>
+    <mergeCell ref="I31:K31"/>
+    <mergeCell ref="A33:K33"/>
+    <mergeCell ref="I34:K34"/>
+    <mergeCell ref="I30:K30"/>
     <mergeCell ref="A5:K5"/>
-    <mergeCell ref="A17:K17"/>
-    <mergeCell ref="A23:K23"/>
+    <mergeCell ref="C30:H30"/>
     <mergeCell ref="C6:K6"/>
-    <mergeCell ref="B14:K14"/>
-    <mergeCell ref="B13:K13"/>
-    <mergeCell ref="C20:H20"/>
-    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="C15:K15"/>
+    <mergeCell ref="B23:K23"/>
+    <mergeCell ref="C14:K14"/>
+    <mergeCell ref="B34:H34"/>
+    <mergeCell ref="C29:H29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
